--- a/therapist_info.xlsx
+++ b/therapist_info.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,7 +713,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Markos Karayianni</t>
+          <t>Habibi Feliciano Perez</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,17 +723,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>“I believe that you are the expert of your story and that you have many strengths that will assist you in overcoming things that challenge you.”</t>
+          <t>“I focus on LGBTQ individuals, couples, and families, where I bring my lived experience as a gay man of Arabic and Latino descent.”</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>https://care.headway.co/providers/markos-karayianni?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+          <t>https://care.headway.co/providers/habibi-feliciano-perez?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Identity issues', 'Relationship issues', 'Transgender issues']</t>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression', 'Family issues']</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -745,7 +745,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Habibi Feliciano Perez</t>
+          <t>Ejay Faralan</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -755,22 +755,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>“I focus on LGBTQ individuals, couples, and families, where I bring my lived experience as a gay man of Arabic and Latino descent.”</t>
+          <t>“My clinical work includes supporting queer, AAPI, and BIPOC individuals with an affirming and culturally responsive approach.”</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>https://care.headway.co/providers/habibi-feliciano-perez?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+          <t>https://care.headway.co/providers/ejay-faralan?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression', 'Family issues']</t>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Bipolar disorder', 'Chronic conditions']</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>['Affirming', 'Empowering', 'Warm']</t>
+          <t>['Direct', 'Humorous', 'Solution-oriented']</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ejay Faralan</t>
+          <t>Jesse Nova</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -819,29 +819,29 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>“My clinical work includes supporting queer, AAPI, and BIPOC individuals with an affirming and culturally responsive approach.”</t>
+          <t>“My goal is to not only make you feel well and be well but to help find your inner strength and thrive in all aspects of life.”</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>https://care.headway.co/providers/ejay-faralan?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+          <t>https://care.headway.co/providers/jesse-nova?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Bipolar disorder', 'Chronic conditions']</t>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression', 'Family issues']</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>['Direct', 'Humorous', 'Solution-oriented']</t>
+          <t>['Affirming', 'Empowering', 'Warm']</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jesse Nova</t>
+          <t>Alexander Graham</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -851,29 +851,29 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>“My goal is to not only make you feel well and be well but to help find your inner strength and thrive in all aspects of life.”</t>
+          <t>“I specialize in supporting people who feel overwhelmed by anxiety, depression, stress, ADHD, trauma, life transitions and much more. I have extensive experience working with high acuity teens, and I also work with adults of all ages who are...”</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>https://care.headway.co/providers/jesse-nova?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+          <t>https://care.headway.co/providers/alexander-graham?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression', 'Family issues']</t>
+          <t>['Matches your filter: LGBTQIA+', 'Anger management', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression']</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>['Affirming', 'Empowering', 'Warm']</t>
+          <t>['Affirming', 'Open-minded', 'Warm']</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alexander Graham</t>
+          <t>Dr. Sky Lea Ross</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -883,29 +883,29 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>“I specialize in supporting people who feel overwhelmed by anxiety, depression, stress, ADHD, trauma, life transitions and much more. I have extensive experience working with high acuity teens, and I also work with adults of all ages who are...”</t>
+          <t>“Operating primarily from a client-centered lens, Dr. Sky views her clients as the experts of their own lives, providing them with empathy, empowerment, and focusing on strengths rather than deficits.”</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>https://care.headway.co/providers/alexander-graham?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+          <t>https://care.headway.co/providers/sky-lea-ross?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>['Matches your filter: LGBTQIA+', 'Anger management', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression']</t>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Bipolar disorder', 'Chronic conditions', 'Cultural &amp; ethnic issues']</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>['Affirming', 'Open-minded', 'Warm']</t>
+          <t>['Affirming', 'Empowering', 'Warm']</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Dr. Sky Lea Ross</t>
+          <t>Elizabeth Gonzalez Morales</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -915,29 +915,29 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>“Operating primarily from a client-centered lens, Dr. Sky views her clients as the experts of their own lives, providing them with empathy, empowerment, and focusing on strengths rather than deficits.”</t>
+          <t>“I am a Latinx, queer, non-binary therapist committed to providing affirming, culturally responsive, and relational care.”</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>https://care.headway.co/providers/sky-lea-ross?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+          <t>https://care.headway.co/providers/elizabeth-gonzalez-morales?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Bipolar disorder', 'Chronic conditions', 'Cultural &amp; ethnic issues']</t>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression']</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>['Affirming', 'Empowering', 'Warm']</t>
+          <t>['Holistic', 'Inquisitive', 'Warm']</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Adrian Conner</t>
+          <t>Stephanie Shepard</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -947,29 +947,29 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>“I believe in meeting you where you are and helping you rewrite your story in a way that empowers you rather than defines you.”</t>
+          <t>“Being a member of the LGBTQ+ community, I have done research on and take a special interest in the negative impacts on mental health for those who suffer from discriminating and internalizing symptoms related to their sexual orientation, identity,...”</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>https://care.headway.co/providers/adrian-conner?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+          <t>https://care.headway.co/providers/stephanie-shepard?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Chronic conditions', 'Grief or loss', 'Identity issues']</t>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression']</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>['Affirming', 'Creative', 'Inquisitive']</t>
+          <t>['Empowering', 'Humorous', 'Open-minded']</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Elizabeth Gonzalez Morales</t>
+          <t>Albert Xiong</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -979,61 +979,61 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>“I am a Latinx, queer, non-binary therapist committed to providing affirming, culturally responsive, and relational care.”</t>
+          <t>“In the (virtual) therapy room, you can expect me to be an animated and relatively lighthearted therapist; I pride myself on bringing my genuine self into our therapeutic relationship, and that's someone who's curious and playful.”</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>https://care.headway.co/providers/elizabeth-gonzalez-morales?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+          <t>https://care.headway.co/providers/albert-xiong?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression']</t>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression', 'Grief or loss']</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>['Holistic', 'Inquisitive', 'Warm']</t>
+          <t>['Direct', 'Humorous', 'Warm']</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Stephanie Shepard</t>
+          <t>Margie Martin</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Therapist, Virtual</t>
+          <t>Therapist, Virtual &amp; in-person</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>“Being a member of the LGBTQ+ community, I have done research on and take a special interest in the negative impacts on mental health for those who suffer from discriminating and internalizing symptoms related to their sexual orientation, identity,...”</t>
+          <t>“I still consider it a rare privilege to sit with clients in this work, especially those carrying grief, navigating a shifting health picture, or trying to rebuild a relationship that no longer fits the life they want.”</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>https://care.headway.co/providers/stephanie-shepard?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+          <t>https://care.headway.co/providers/margie-martin?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression']</t>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Depression', 'Grief or loss']</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>['Empowering', 'Humorous', 'Open-minded']</t>
+          <t>['Empowering', 'Inquisitive', 'Open-minded']</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Albert Xiong</t>
+          <t>Rachelle Bodle</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1043,61 +1043,61 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>“In the (virtual) therapy room, you can expect me to be an animated and relatively lighthearted therapist; I pride myself on bringing my genuine self into our therapeutic relationship, and that's someone who's curious and playful.”</t>
+          <t>“I'm dedicated to cultivating positivity, strength, and resilience in my clients for a healthier, more balanced life.”</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>https://care.headway.co/providers/albert-xiong?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+          <t>https://care.headway.co/providers/rachelle-bodle?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression', 'Grief or loss']</t>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Depression', 'PTSD', 'Trauma']</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>['Direct', 'Humorous', 'Warm']</t>
+          <t>['Affirming', 'Empowering', 'Solution-oriented']</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Margie Martin</t>
+          <t>Ashley Walay</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Therapist, Virtual &amp; in-person</t>
+          <t>Therapist, Virtual</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>“I still consider it a rare privilege to sit with clients in this work, especially those carrying grief, navigating a shifting health picture, or trying to rebuild a relationship that no longer fits the life they want.”</t>
+          <t>“You’re capable and use to managing a lot, but lately life feels overwhelming.I’m Ashley Walay, LICSW, and I work with BIPOC women and LGBTQ+ individuals, professionals, single parents, and military-connected individuals (including spouses, veterans,...”</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>https://care.headway.co/providers/margie-martin?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+          <t>https://care.headway.co/providers/ashley-walay?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Depression', 'Grief or loss']</t>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Bipolar disorder', 'Depression']</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>['Empowering', 'Inquisitive', 'Open-minded']</t>
+          <t>['Direct', 'Holistic', 'Open-minded']</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Rachelle Bodle</t>
+          <t>Amber Boyd</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1107,29 +1107,29 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>“I'm dedicated to cultivating positivity, strength, and resilience in my clients for a healthier, more balanced life.”</t>
+          <t>“I specialize in working with individuals who hold multiple intersecting identities, including Black, LGBTQ+, and other historically marginalized communities...”</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>https://care.headway.co/providers/rachelle-bodle?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+          <t>https://care.headway.co/providers/amber-boyd-2?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Depression', 'PTSD', 'Trauma']</t>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression', 'Identity issues']</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>['Affirming', 'Empowering', 'Solution-oriented']</t>
+          <t>['Affirming', 'Challenging', 'Empowering']</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ashley Walay</t>
+          <t>Kate Salami</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1139,61 +1139,56 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>“You’re capable and use to managing a lot, but lately life feels overwhelming.I’m Ashley Walay, LICSW, and I work with BIPOC women and LGBTQ+ individuals, professionals, single parents, and military-connected individuals (including spouses, veterans,...”</t>
+          <t>“I provide an inclusive, empathetic, and nonjudgmental space that welcomes people of all genders, sexual orientations, and religious backgrounds.”</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://care.headway.co/providers/ashley-walay?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+          <t>https://care.headway.co/providers/kate-salami?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Bipolar disorder', 'Depression']</t>
+          <t>['Matches your filter: LGBTQIA+', 'Anger management', 'Anxiety', 'Bipolar disorder', 'Depression']</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>['Direct', 'Holistic', 'Open-minded']</t>
+          <t>['Empowering', 'Open-minded', 'Participatory']</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Amber Boyd</t>
+          <t>Almog Shanun</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Therapist, Virtual</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>“I specialize in working with individuals who hold multiple intersecting identities, including Black, LGBTQ+, and other historically marginalized communities...”</t>
+          <t>Therapist, Virtual &amp; in-person</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://care.headway.co/providers/amber-boyd-2?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+          <t>https://care.headway.co/providers/almog-shanun?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression', 'Identity issues']</t>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Bipolar disorder']</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>['Affirming', 'Challenging', 'Empowering']</t>
+          <t>['Challenging', 'Empowering', 'Holistic']</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Kate Salami</t>
+          <t>Markos Karayianni</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1203,56 +1198,61 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>“I provide an inclusive, empathetic, and nonjudgmental space that welcomes people of all genders, sexual orientations, and religious backgrounds.”</t>
+          <t>“I believe that you are the expert of your story and that you have many strengths that will assist you in overcoming things that challenge you.”</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://care.headway.co/providers/kate-salami?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+          <t>https://care.headway.co/providers/markos-karayianni?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>['Matches your filter: LGBTQIA+', 'Anger management', 'Anxiety', 'Bipolar disorder', 'Depression']</t>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Identity issues', 'Relationship issues', 'Transgender issues']</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>['Empowering', 'Open-minded', 'Participatory']</t>
+          <t>['Affirming', 'Empowering', 'Warm']</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Almog Shanun</t>
+          <t>Lucas Dangler</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Therapist, Virtual &amp; in-person</t>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>“I value lifelong learning, openness to new experiences, curiosity about the self and the world, and working to enhance our capacity for compassion for ourselves and others, individually and collectively.”</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://care.headway.co/providers/almog-shanun?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+          <t>https://care.headway.co/providers/lucas-dangler?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Bipolar disorder']</t>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Depression', 'Family issues', 'Grief or loss']</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>['Challenging', 'Empowering', 'Holistic']</t>
+          <t>['Direct', 'Holistic', 'Open-minded']</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Lucas Dangler</t>
+          <t>Priscilla Conkrite</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1262,29 +1262,29 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>“I value lifelong learning, openness to new experiences, curiosity about the self and the world, and working to enhance our capacity for compassion for ourselves and others, individually and collectively.”</t>
+          <t>“My approach in therapy is client-centered and holistic, to help you identify your strengths and develop new skills and interventions to improve the quality of your daily living.”</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://care.headway.co/providers/lucas-dangler?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+          <t>https://care.headway.co/providers/priscilla-conkrite?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Depression', 'Family issues', 'Grief or loss']</t>
+          <t>['Matches your filter: LGBTQIA+', 'Anger management', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression']</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>['Direct', 'Holistic', 'Open-minded']</t>
+          <t>['Affirming', 'Open-minded', 'Solution-oriented']</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Priscilla Conkrite</t>
+          <t>Oscar Droege-Sanchez</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1294,29 +1294,29 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>“My approach in therapy is client-centered and holistic, to help you identify your strengths and develop new skills and interventions to improve the quality of your daily living.”</t>
+          <t>“I am a Licensed Clinical Social Worker (LCSW) and Certified Addiction Treatment Counselor-IV (CATC-IV) with experience working in mental health for the last 4 years and substance use treatment, including LGBTQIA(plus) affirming and dual-diagnosis...”</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://care.headway.co/providers/priscilla-conkrite?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+          <t>https://care.headway.co/providers/oscar-droege-sanchez?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>['Matches your filter: LGBTQIA+', 'Anger management', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression']</t>
+          <t>['Matches your filter: LGBTQIA+', 'Anger management', 'Anxiety', 'Depression', "Men's issues"]</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>['Affirming', 'Open-minded', 'Solution-oriented']</t>
+          <t>['Affirming', 'Empowering', 'Open-minded']</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Oscar Droege-Sanchez</t>
+          <t>Hanna Jeong</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1326,29 +1326,29 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>“I am a Licensed Clinical Social Worker (LCSW) and Certified Addiction Treatment Counselor-IV (CATC-IV) with experience working in mental health for the last 4 years and substance use treatment, including LGBTQIA(plus) affirming and dual-diagnosis...”</t>
+          <t>“I am especially passionate about validating and affirming the lived experiences of LGBTQIA+ and BIPOC communities.”</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://care.headway.co/providers/oscar-droege-sanchez?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+          <t>https://care.headway.co/providers/hanna-jeong?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>['Matches your filter: LGBTQIA+', 'Anger management', 'Anxiety', 'Depression', "Men's issues"]</t>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression']</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>['Affirming', 'Empowering', 'Open-minded']</t>
+          <t>['Empowering', 'Holistic', 'Open-minded']</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hanna Jeong</t>
+          <t>Danielle Rhinesmith</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1358,29 +1358,29 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>“I am especially passionate about validating and affirming the lived experiences of LGBTQIA+ and BIPOC communities.”</t>
+          <t>“Hello! My name is Danielle, and I have been a licensed Marriage and Family Therapist for over 10 years. Too often, we can become overwhelmed by the pressures of life, and that is where therapy can help. It may be time to prioritize your own mental...”</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://care.headway.co/providers/hanna-jeong?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+          <t>https://care.headway.co/providers/danielle-rhinesmith?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression']</t>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Bipolar disorder']</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>['Empowering', 'Holistic', 'Open-minded']</t>
+          <t>['Affirming', 'Humorous', 'Open-minded']</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Danielle Rhinesmith</t>
+          <t>Julia Alperovich</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1390,29 +1390,29 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>“Hello! My name is Danielle, and I have been a licensed Marriage and Family Therapist for over 10 years. Too often, we can become overwhelmed by the pressures of life, and that is where therapy can help. It may be time to prioritize your own mental...”</t>
+          <t>“I hold the belief that people are resilient and that they possess the strength and wisdom to heal seemingly irreparable wounds.”</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://care.headway.co/providers/danielle-rhinesmith?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+          <t>https://care.headway.co/providers/julia-alperovich?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Bipolar disorder']</t>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Depression', 'Family issues']</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>['Affirming', 'Humorous', 'Open-minded']</t>
+          <t>['Direct', 'Empowering', 'Participatory']</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Julia Alperovich</t>
+          <t>Aurora Graham</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1422,29 +1422,29 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>“I hold the belief that people are resilient and that they possess the strength and wisdom to heal seemingly irreparable wounds.”</t>
+          <t>“Do you feel stuck or overwhelmed by circumstances that feel impossible? I help people get unstuck from what’s holding them back. My goal is for you to have more freedom and live an authentic, fulfilling life. We’ll work together to create a...”</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://care.headway.co/providers/julia-alperovich?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+          <t>https://care.headway.co/providers/aurora-graham?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Depression', 'Family issues']</t>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Chronic conditions', 'Cultural &amp; ethnic issues', 'Depression']</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>['Direct', 'Empowering', 'Participatory']</t>
+          <t>['Direct', 'Open-minded', 'Warm']</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Aurora Graham</t>
+          <t>Mark Casas</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1454,29 +1454,29 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>“Do you feel stuck or overwhelmed by circumstances that feel impossible? I help people get unstuck from what’s holding them back. My goal is for you to have more freedom and live an authentic, fulfilling life. We’ll work together to create a...”</t>
+          <t>“I believe everyone has the ability to heal and grow, and my role is to create a safe, affirming space where that process feels possible.”</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://care.headway.co/providers/aurora-graham?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+          <t>https://care.headway.co/providers/mark-casas?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Chronic conditions', 'Cultural &amp; ethnic issues', 'Depression']</t>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Depression', 'Family issues', 'Grief or loss']</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>['Direct', 'Open-minded', 'Warm']</t>
+          <t>['Affirming', 'Creative', 'Empowering']</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Mark Casas</t>
+          <t>Emily McKillip</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1486,29 +1486,29 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>“I believe everyone has the ability to heal and grow, and my role is to create a safe, affirming space where that process feels possible.”</t>
+          <t>“I am known for creating a warm, safe, and collaborative therapeutic space where clients feel seen, heard, and empowered to heal.”</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://care.headway.co/providers/mark-casas?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+          <t>https://care.headway.co/providers/emily-mckillip?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Depression', 'Family issues', 'Grief or loss']</t>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Depression', 'Relationship issues', 'Substance use / addiction']</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>['Affirming', 'Creative', 'Empowering']</t>
+          <t>['Holistic', 'Open-minded', 'Solution-oriented']</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Emily McKillip</t>
+          <t>Adrian Conner</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1518,22 +1518,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>“I am known for creating a warm, safe, and collaborative therapeutic space where clients feel seen, heard, and empowered to heal.”</t>
+          <t>“I believe in meeting you where you are and helping you rewrite your story in a way that empowers you rather than defines you.”</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://care.headway.co/providers/emily-mckillip?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+          <t>https://care.headway.co/providers/adrian-conner?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Depression', 'Relationship issues', 'Substance use / addiction']</t>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Chronic conditions', 'Grief or loss', 'Identity issues']</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>['Holistic', 'Open-minded', 'Solution-oriented']</t>
+          <t>['Affirming', 'Creative', 'Inquisitive']</t>
         </is>
       </c>
     </row>
@@ -2116,39 +2116,39 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Dr. Alexis Wong</t>
+          <t>Imani Francis</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Psychologist, Virtual</t>
+          <t>Therapist, Virtual</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>“My hope is that sessions with me are warm, challenging, thought-provoking and thoughtful, so expect sessions to include tears, laughter and profound moments of appreciation for life, its difficulties and rewards.”</t>
+          <t>“As a Black cisgender woman, I bring lived experience and genuine cultural understanding to my work — especially with BIPOC clients, women of color, and LGBTQIA+ individuals who are looking for a therapist who truly gets it without needing an...”</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://care.headway.co/providers/alexis-wong?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+          <t>https://care.headway.co/providers/imani-francis-2?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>['Matches your filter: LGBTQIA+', 'Anger management', 'Bipolar disorder', 'Cultural &amp; ethnic issues', 'Depression']</t>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression', 'Family issues']</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>['Empowering', 'Inquisitive', 'Warm']</t>
+          <t>['Empowering', 'Holistic', 'Humorous']</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Imani Francis</t>
+          <t>Chelsey West</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2158,54 +2158,54 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>“As a Black cisgender woman, I bring lived experience and genuine cultural understanding to my work — especially with BIPOC clients, women of color, and LGBTQIA+ individuals who are looking for a therapist who truly gets it without needing an...”</t>
+          <t>“I use a blend of CBT, DBT, and ACT to help you build practical skills while also exploring the deeper patterns that may be holding you back.”</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://care.headway.co/providers/imani-francis-2?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+          <t>https://care.headway.co/providers/chelsey-west?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression', 'Family issues']</t>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Bipolar disorder', 'Cultural &amp; ethnic issues']</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>['Empowering', 'Holistic', 'Humorous']</t>
+          <t>['Challenging', 'Humorous', 'Warm']</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Chelsey West</t>
+          <t>Dr. Alexis Wong</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Therapist, Virtual</t>
+          <t>Psychologist, Virtual</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>“I use a blend of CBT, DBT, and ACT to help you build practical skills while also exploring the deeper patterns that may be holding you back.”</t>
+          <t>“My hope is that sessions with me are warm, challenging, thought-provoking and thoughtful, so expect sessions to include tears, laughter and profound moments of appreciation for life, its difficulties and rewards.”</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://care.headway.co/providers/chelsey-west?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+          <t>https://care.headway.co/providers/alexis-wong?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Bipolar disorder', 'Cultural &amp; ethnic issues']</t>
+          <t>['Matches your filter: LGBTQIA+', 'Anger management', 'Bipolar disorder', 'Cultural &amp; ethnic issues', 'Depression']</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>['Challenging', 'Humorous', 'Warm']</t>
+          <t>['Empowering', 'Inquisitive', 'Warm']</t>
         </is>
       </c>
     </row>
@@ -2398,6 +2398,5766 @@
       <c r="F61" t="inlineStr">
         <is>
           <t>['Affirming', 'Direct', 'Open-minded']</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Mercy Flores Isaac</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>“I'm direct, warm, and genuinely collaborative. I don't believe in a one-size-fits-all approach to therapy, so I'll adapt our work to what actually fits your life, your pace, and your goals.”</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/mercy-flores-isaac?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Depression', 'Family issues', 'Grief or loss']</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>['Direct', 'Solution-oriented', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Mallory Garrett</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>“My therapeutic approach centers on meeting you where you are and fostering a collaborative environment to address the issues causing you distress.”</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/mallory-garrett-2?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Depression', 'Diabetes']</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Creative', 'Inquisitive']</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Xiomara Morales</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>“I believe healing occurs when we address the connection between the mind, body, nervous system, and spirit while building on each person's existing strengths and resilience.”</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/xiomara-morales?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Bipolar disorder', 'Cultural &amp; ethnic issues']</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>['Direct', 'Empowering', 'Holistic']</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Brian Wolfe</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>“I do enjoy working with engaged individuals, teenagers, couples and families interested in learning more about themselves and their relationships in the world.”</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/brian-wolfe?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Bipolar disorder']</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>['Creative', 'Open-minded', 'Solution-oriented']</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Dr. John W. Carter</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Psychologist, Virtual &amp; in-person</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>“I am a recently licensed counseling psychologist with extensive training and experience in psychotherapy, assessment, and psychology research. I have provided individual, couples, and group therapy at the Los Angeles Gay &amp; Lesbian Center (now LGBT...”</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/john-w-carter?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Bipolar disorder']</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>['Direct', 'Empowering', 'Open-minded']</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Ashley Steineckert</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>“I believe meaningful change happens when people feel safe enough to be honest about what's hard, confusing, or painful — and also when they feel challenged in thoughtful and compassionate ways.”</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/ashley-steineckert?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Depression', 'Family issues', 'Grief or loss']</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>['Energetic', 'Open-minded', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Talia Guppy</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>“Welcome! I am currently accepting client and I specialize in working with LGBTQ+ adolescents and young adults, providing affirming care through a solution‐focused and client‐centered approach. I utilize Cognitive Behavioral Therapy (CBT) to help...”</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/talia-guppy?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Bipolar disorder']</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Energetic', 'Solution-oriented']</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Evan Dunn</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>“I encourage profound exploration of symptoms and conflicts while simultaneously offering my patients a space of warmth and relief in which to grow.”</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/evan-dunn?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anger management', 'Anxiety', 'Depression', 'Eating disorders']</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>['Creative', 'Humorous', 'Inquisitive']</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Claire Morrison</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>“I’ve worked as a therapist for the past ten years, helping people untangle their stories and find compassion for the messy, imperfect parts of being human. My own experiences as a client deeply shaped my approach. I bring empathy, warmth, and a...”</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/claire-morrison?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Depression', 'Family issues']</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>['Humorous', 'Open-minded', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Jaime DiMeco</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>“I'm Jaime DiMeco &amp; I'm honored that you're here. I've been a psychotherapist since 2018, &amp; have the privilege to serve clients of all backgrounds - with a variety of therapeutic needs &amp; goals - struggling through difficult seasons of life. I am...”</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/jaime-dimeco?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression']</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Empowering', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Chelsie Norton</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>“Having spent many years involved in alternative culture, I support client's in addressing issues around non traditional partnerships/lifestyles, substance use, trauma histories and major life transitions.”</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/chelsie-norton?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression', 'Family issues']</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>['Holistic', 'Inquisitive', 'Open-minded']</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Lili Kroutilina</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>“I specialize in trauma-informed, integrative, holistic modalities for anxiety, ADHD, stress/burn-out, life transitions, relationships, grief, and depression with adults, couples, LGBTQ+, BIPOC, and alternative lifestyles”</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/lili-kroutilina?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression']</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>['Empowering', 'Holistic', 'Open-minded']</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Tone Va'i</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>“I'm direct, relational, and reflective in how I work. I started in early childhood mental health, which shaped how I understand people.”</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/tone-va-i?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression', 'Family issues']</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Direct', 'Open-minded']</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Dr. Marci Kyle</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>“I believe in focusing on client's strengths rather than pathology and guiding clients to create the right condition for themselves to reach their goals...”</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/marci-kyle?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anger management', 'Anxiety', 'Bipolar disorder', 'Chronic conditions']</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Empowering', 'Holistic']</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Shawn Roth</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>“My own mental health journey was aided by the help of some amazing mental health professionals, and since that time I have been working towards helping others understand themselves in the way that I was helped.”</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/shawn-roth?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Chronic conditions', 'Depression']</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Empowering', 'Inquisitive']</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Hollis Wiese</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>“Hollis Wiese, LMFT has extensive experience treating adults, teens, and couples. Hollis approaches the therapeutic experience from a client-centered, LGBTQIA+-affirmative, and sex-positive place. Hollis uses warmth, humor, and open-mindedness to...”</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/hollis-wiese?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Bipolar disorder']</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>['Humorous', 'Open-minded', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Deborah Ebrahemi</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>“I specialize in working with adolescents, families, young adults, postpartum parents and LGBTQIA+ individuals who are struggling with anxiety, depression, school stressors, parenting stressors, life transitions, postpartum, and relationships.”</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/deborah-ebrahemi?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Depression', 'Relationship issues', 'Stress management']</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>['Holistic', 'Open-minded', 'Solution-oriented']</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>America Islas</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>“Tired of feeling like you have to educate your therapist before you can actually begin? You deserve a therapist who actively celebrates who you are. I specialize in LGBTQI2-S affirmative care and work with individuals, couples, and families...”</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/america-islas-2?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression', 'Family issues']</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Empowering', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Olivia White</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>“I believe that true healing requires accessing stored trauma in the body and helping your nervous system to feel safe.”</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/olivia-white-3?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Depression', 'Eating disorders']</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>['Holistic', 'Open-minded', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Cindi Lane-Pompa</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>“I specialize in working with neurodivergent adults (ADHD, autism), LGBTQIA individuals, and those navigating chronic illness, burnout, and perimenopause or menopause. Many of my clients come to therapy feeling overwhelmed, exhausted, or like nothing...”</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/cindi-lane-pompa?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Chronic conditions', 'Depression']</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>['Humorous', 'Open-minded', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Dr. Lynelle Tyler</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Psychologist, Virtual</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>“My therapeutic approach is solution-focused and strength based. We use your strengths to bolster other aspects of your life.”</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/lynelle-tyler?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Chronic conditions', 'End of life care']</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>['Creative', 'Empowering', 'Solution-oriented']</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Corrine Thomas</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>“I specialize in helping clients navigate depression, anxiety, anger, trauma, and the thought patterns that keep them feeling stuck. Since 2003, I’ve used CBT informed, trauma informed, and solution focused techniques to help clients understand...”</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/corrine-thomas-2?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anger management', 'Anxiety', 'Depression', 'Grief or loss']</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>['Challenging', 'Direct', 'Humorous']</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Natalie Espinoza</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>“I bring a warm, grounded presence and create a space where your nervous system can settle so you feel safe enough to be fully yourself and understood.”</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/natalie-espinoza?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Chronic conditions', 'Depression', 'Grief or loss']</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>['Empowering', 'Open-minded', 'Participatory']</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Laura Morgan</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>“I strive to address bias and embrace diversity while being open to learning how each person's race, culture, gender, sexuality, class and identity impacts their life.”</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/laura-morgan?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Depression', 'Grief or loss', 'Identity issues']</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Holistic', 'Open-minded']</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>James Johansen</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>“My approach is rooted in compassion and evidence-based methodologies. In a confidential, nonjudgmental, trauma-informed environment, we collaboratively identify barriers and develop practical strategies to foster fulfilling and confident...”</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/james-johansen?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anger management', 'Anxiety', 'Depression', 'End of life care']</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>['Direct', 'Empowering', 'Open-minded']</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Maranda Garnett</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>“I provide a gender affirming, person centered, and trauma informed approach to create a safe space for you to be vulnerable...”</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/maranda-garnett?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Bipolar disorder']</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>['Humorous', 'Open-minded', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Christina Spektor</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>“I believe people make sense in the context of their experiences, and therapy offers an opportunity to understand those experiences with curiosity rather than self-criticism.”</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/christina-spektor?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression']</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Open-minded', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Tanaya Reid</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>“I like to create a comforting and welcoming environment where it feels safe to talk about and try difficult things.”</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/tanaya-reid?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Cultural &amp; ethnic issues']</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>['Direct', 'Holistic', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Ben Quan</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>“Hello! I am a Licensed Clinical Social Worker (LCSW) with almost 10 years experience providing individual therapy. I am a graduate of Cal State Fullerton, and specialize in EMDR therapy and LGBTQ+ affirming therapy. I am a big advocate for taking...”</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/ben-quan?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression', 'Family issues']</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Inquisitive', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Amada Adame</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>“My approach is integrative, combining a strengths-based approach along with trauma informed therapies.”</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/amada-adame?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anger management', 'Anxiety', 'Bipolar disorder', 'Cultural &amp; ethnic issues']</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>['Holistic', 'Open-minded', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Jessica Saucedo</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>“I utilize a person-centered approach. It is important for the person I am working with to feel heard.”</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/jessica-saucedo?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Bipolar disorder', 'Depression']</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Open-minded', 'Participatory']</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Levin Manabat</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>“My approach is compassionate, collaborative, and evidence-based, integrating trauma-informed care with therapies tailored to your unique goals and experiences.”</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/levin-manabat?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Bipolar disorder']</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>['Holistic', 'Open-minded', 'Solution-oriented']</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Kimberly Porter-Leite</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>“I have a deep belief in the healing power of relationship and draw from a range of trauma-informed, somatic, depth and behavioral approaches in my work.”</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/kimberly-porter-leite?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Depression', 'End of life care', 'Grief or loss']</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>['Holistic', 'Open-minded', 'Participatory']</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Erick Nunez</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>“Change can be scary but so is staying the same. There is a quote that I live by "Whatever you are not changing ... you are choosing".”</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/erick-nunez?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Depression']</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>['Direct', 'Empowering', 'Humorous']</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Alexandra Anguiano</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>“I am trained in EMDR, which helps people process and heal from painful or overwhelming experiences that may still be affecting them today.”</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/alexandra-anguiano?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Depression', 'Family issues']</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Creative', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Natalya Sivashov</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>“I lived in 3 different countries throughout my formative years which has inspired in me a love for multiculturalism, open-heartedness, resilience, and a passion for helping people heal.”</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/natalya-sivashov?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Family issues', 'PTSD']</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>['Holistic', 'Open-minded', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Allison Trujillo</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>“I use a mix of DBT, EMDR, and IFS to help people explore the deeper layers of their story—especially around trauma, identity, and body image.”</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/allison-trujillo?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression']</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Open-minded', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Maximiliano Cabellos</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual &amp; in-person</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>“Hi My name is Maximiliano Cabellos, LMFT I am here to support you in addressing your needs and help you discover an appropriate and healthy approach. My goal is to assist you in getting to the root of challenges and overcoming them to live a more...”</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/maximiliano-cabellos?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Bipolar disorder']</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>['Holistic', 'Humorous', 'Inquisitive']</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Robin Mathy</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>“I provide a space rooted in safety, deep listening, and compassion. Healing is a sacred journey—a process of growing insight, clarity, and wisdom while reclaiming wholeness and transforming pain into purpose. Together, we can explore the paths that...”</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/robin-mathy?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Bipolar disorder']</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Open-minded', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Desiree Joslyn</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>“I specialize in working with neurodivergent individuals and their families, helping to create understanding, support, and meaningful connections.”</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/desiree-joslyn?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Depression']</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>['Empowering', 'Humorous', 'Open-minded']</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Dr. Ashley Gerken</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>“My style is warm, direct, and insight-oriented, balancing deep emotional work with practical tools for change.”</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/ashley-gerken?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anger management', 'Family issues', 'PTSD', 'Relationship issues']</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Empowering', 'Solution-oriented']</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Julián Aguilar-Hernández</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>“I bring over 15 years of clinical practice working with adults, adolescents, and families in English and Spanish on life transitions and crisis work.”</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/julian-aguilar-hernandez?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression']</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>['Humorous', 'Open-minded', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Alea Holman</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Psychologist, Virtual</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>“I believe meaningful growth begins when you can show up fully as yourself and feel supported in the process.”</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/alea-holman?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression']</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Inquisitive', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Dr. Lisa Cooney</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>“You're trauma-informed, attuned to nervous systems, and you understand recovery, resilience, and transformation not just academically, but lived and embodied.”</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/lisa-cooney-2?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression', 'Eating disorders']</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>['Direct', 'Empowering', 'Humorous']</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Johnny Valera</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>“My style is grounded in compassion, humor, and empowerment, creating a low-pressure environment where clients feel comfortable progressing at their own pace.”</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/johnny-valera?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anger management', 'Anxiety', 'Chronic conditions', 'Cultural &amp; ethnic issues']</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Empowering', 'Humorous']</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Emily Campbell</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>“I believe therapy should be a safe space where you feel heard, understood, and empowered to move toward the life you want.”</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/emily-campbell-2?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Chronic conditions', 'Depression']</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Open-minded', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Michelle Michicoff</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>“My path to becoming a therapist was shaped by my own personal experiences and my interests in human behavior, attachment theory, and social justice. My nearly six years of experience working in community mental health have strongly influenced my...”</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/michelle-michicoff?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Chronic conditions', 'Cultural &amp; ethnic issues']</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Direct', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Kelsey Gates</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>“I bring creativity into sessions and strive to create a space that feels safe enough to be transformative.”</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/kelsey-gates?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Depression', 'Family issues', 'Identity issues']</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>['Creative', 'Empowering', 'Holistic']</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Ann Legierski</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>“Rather than just focusing on symptoms, my goal is to foster a sense of curiosity and self-awareness that allows you to heal and grow at your own pace.”</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/ann-legierski?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Bipolar disorder']</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>['Empowering', 'Humorous', 'Open-minded']</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Virginia Sanchez</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>“Welcome to Bright House Therapy, LLC. My name is Virginia Sanchez, I am a Licensed Marriage and Family Therapist with several years of experience working in LGBTQIA+, Grief &amp; Loss, Bipolar, Trauma, ADHD, and Autism. I have worked in several...”</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/virginia-sanchez?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Bipolar disorder', 'Depression']</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Open-minded', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Macayla Meyers</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>“At the core of my work is the belief that the relationship you have with yourself shapes every other relationship in your life.”</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/macayla-meyers?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Bipolar disorder', 'Chronic conditions']</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Challenging', 'Open-minded']</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Xing Liu</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>“In terms of evidence-based approaches, I use Cognitive Behavioral Therapy (CBT), Dialectical Behavior Therapy (DBT) and Motivational Interviewing.”</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/xing-liu?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Cultural &amp; ethnic issues']</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>['Empowering', 'Open-minded', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Cynthia Fullwood-fleck</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>“I believe that therapy is a collaborative journey—one where you show up as your authentic self and know that you'll be supported every step of the way.”</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/cynthia-fullwood-fleck?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression', 'Family issues']</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Open-minded', 'Solution-oriented']</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Velvet Tabb</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>“My goal is to empower clients to face their fears, reduce distress, and move toward a life that is guided by their values rather than their anxiety.”</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/velvet-tabb?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Depression', 'Grief or loss', 'Identity issues']</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Humorous', 'Open-minded']</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Percival Fisher</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>“Client's have shared with me that at the end of each our session together that they have felt heard, validated, and respected.”</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/percival-fisher?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression', 'Grief or loss']</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Direct', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Jonathan Klein</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual &amp; in-person</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>“I'm a Marriage and Family Therapist based in Los Angeles and love this work. I came to therapy through an unconventional path — nearly a decade in film and photography, work as a youth counselor, and service in the military — all of which deeply...”</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/jonathan-klein?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anger management', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression']</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>['Humorous', 'Solution-oriented', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Kianna Romero</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>“I am a Licensed Clinical Social Worker and I have experience working with minority populations, mainly with the Latinx community as well as LGBTQIA+ community.”</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/kianna-romero?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Chronic conditions']</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>['Empowering', 'Open-minded', 'Solution-oriented']</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Bradford Noble</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>“My approach is collaborative, compassionate, and empowering, grounded in multicultural counseling and social justice education...”</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/bradford-noble?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Bipolar disorder', 'Depression']</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>['Direct', 'Solution-oriented', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Lisa Friedman</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>“I believe that you already have information as to what will help you in your journey. It is my job to help you get to the answers...”</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/lisa-friedman-4?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Bipolar disorder', 'Chronic conditions']</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>['Open-minded', 'Participatory', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Dr. Scott Ivey</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Psychologist, Virtual</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>“During sessions, I prioritize listening to you approximately 80% of the time and provide feedback on the remaining 20%.”</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/scott-ivey?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Depression', 'Grief or loss', "Men's issues"]</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Participatory', 'Solution-oriented']</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Erin Zamora</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>“My goal is to create a calm, collaborative space where you feel seen, respected, and empowered to move forward at your own pace.”</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/erin-zamora?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anger management', 'Anxiety', 'Depression', 'Relationship issues']</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>['Humorous', 'Open-minded', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Eunique LeGuie</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>“I work with BIPOC women navigating maternal mental health, grief, and the identity shifts that can quietly unravel what you thought you knew about yourself.”</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/eunique-leguie?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anger management', 'Anxiety', 'Bipolar disorder', 'Chronic conditions']</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Empowering', 'Open-minded']</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Michael Kessler</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>“I believe you are the expert on you, not me! I take a collaborative, client-centered &amp; humanistic approach to therapy.”</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/michael-kessler?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression', 'Identity issues']</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Empowering', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Maria Herrera</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>“I see therapy as a collaboration between the therapist and the client. You are the expert in your life.”</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/maria-herrera-3?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Chronic conditions', 'Cultural &amp; ethnic issues', 'Depression']</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>['Humorous', 'Open-minded', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Dr. Robin Hilliard Albertson</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>“Everyone is worthy and deserving of respect, kindness, compassion, and consideration. That's at the core of how I approach care...”</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/robin-hilliard-albertson?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Cultural &amp; ethnic issues', 'Family issues', 'Identity issues']</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>['Empowering', 'Holistic', 'Humorous']</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Ewan Duarte</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>“Now accepting new clients. I am a transgender man and queer identified. Before becoming a therapist, I had previous work experience and years of study as a creative professional and educator. I value authenticity, a willingness and openness to...”</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/ewan-duarte?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Depression', 'Family issues', 'Grief or loss']</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Holistic', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Kimberly Tinsley</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>“My approach is warm, direct, and holistic, and I genuinely love getting to know the people I work with.”</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/kimberly-tinsley?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Bipolar disorder', 'Depression', 'Family issues']</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>['Direct', 'Holistic', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Bonnie Gordon</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>“I work collaboratively with clients, and firmly believe that clients are the experts on their own lived experience.”</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/bonnie-gordon?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anger management', 'Anxiety', 'Chronic conditions', 'Cultural &amp; ethnic issues']</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>['Empowering', 'Open-minded', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Alexis McFarlin</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>“As a Licensed Professional Clinical Counselor and someone who has lived and thrived in polyamorous relationships for the past eight years...”</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/alexis-mcfarlin?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Depression', 'Family issues']</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>['Empowering', 'Open-minded', 'Solution-oriented']</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Borzu Davarpanah</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>“I can help you reach your true potential. Together we can heal the wounds that keep you feeling stuck, unable to change.”</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/borzu-davarpanah?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Bipolar disorder', 'Depression', "Men's issues"]</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>['Empowering', 'Open-minded', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Theresa Searles</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>“My goal is to work with my clients to increase self-empowerment and learn new tools to overcome life challenges.”</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/theresa-searles?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Bipolar disorder']</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>['Holistic', 'Inquisitive', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Jessica Rosas</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>“My style is warm, collaborative, and grounded. I'll meet you where you are, and together we'll set goals that matter to you.”</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/jessica-rosas?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Bipolar disorder', 'Cultural &amp; ethnic issues']</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>['Empowering', 'Humorous', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Bonni Funk</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>“I've had over 20 years experience in helping people heal from co-dependency, particularly from those with narcissistic behaviors.”</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/bonni-funk?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Bipolar disorder']</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>['Inquisitive', 'Open-minded', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Alex Rhodes</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>“Finding and embracing your authentic self is a journey that can be challenging. Figuring out how to cope in a healthy way with what the world throws at us can be difficult. I'm interested in working with you to figure out how you want your life and...”</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/alex-rhodes?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Chronic conditions', 'Cultural &amp; ethnic issues', 'Depression']</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>['Creative', 'Empowering', 'Open-minded']</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Veronica Michael</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>“I have completed a MA in Counseling Psychology. I have worked with diverse populations covering many issues. My approach is client focused through active listening skills and empathic support.”</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/veronica-michael?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anger management', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression']</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Open-minded', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Jeff J Garcia</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>“I offer a supportive, nonjudgmental space in both English and Spanish where you can feel truly heard and empowered.”</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/jeff-j-garcia?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Bipolar disorder']</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Empowering', 'Solution-oriented']</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Nathan Thephavongsa</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>“My approach is warm, open-minded, and collaborative. I believe therapy is a space for exploration and growth...”</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/nathan-thephavongsa?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Depression', 'PTSD', 'Relationship issues']</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>['Direct', 'Open-minded', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Jose Hernandez</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>“I’m a naturally curious, growth-oriented human who believes healing happens when insight meets action. I love helping people zoom out to see the bigger picture of their lives—while also gently zooming in on the patterns, habits, and beliefs that...”</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/jose-hernandez-3?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anger management', 'Anxiety', 'Chronic conditions', 'Cultural &amp; ethnic issues']</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Holistic', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Angie Gunn</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>“Hey you, I'm Angie, an AASECT Certified Sex Therapist and supervisor, with more than 15 years experience in the sexuality field, supporting sexuality communities, and teaching others to break the sex and gender boxes we were given. In addition to my...”</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/angie-gunn?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Depression', 'Family issues']</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Creative', 'Open-minded']</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Fizura Barker</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Psychologist, Virtual</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>“Sometimes the hardest part isn't the struggle itself. It's finding someone who will actually understand the world you're living in. I'm Pia, a psychotherapist with many years of experience working with adults and seniors through anxiety, trauma,...”</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/fizura-barker?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression', 'Family issues']</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Empowering', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Dr. Kourtney Carter</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>“I believe mental health should be embraced, prioritized, and treated with the same importance as physical health.”</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/kourtney-carter?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Bipolar disorder', 'Cultural &amp; ethnic issues', 'Depression']</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>['Open-minded', 'Solution-oriented', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Melony Burns</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>“I appreciate the eclectic person you are and would like to help you identify your own cracks, so that you can let your own light in.”</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/melony-burns?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Depression', 'Diabetes', 'Identity issues']</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Open-minded', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Riva Orr</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>“My clients can expect the "detective work" approach of CBT coupled with the more experimental approach, such as reenacting dreams and parts work.”</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/riva-orr?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Chronic conditions', 'Cultural &amp; ethnic issues']</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>['Creative', 'Holistic', 'Inquisitive']</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Maria Martinez</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>“My style is warm, collaborative, and culturally responsive. As a Mexican-American Latina and daughter of immigrant parents, I understand how culture, family expectations, and lived experiences can shape emotional well-being.”</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/maria-martinez-6?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression', 'Family issues']</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>['Empowering', 'Open-minded', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Andrea Faraday</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>“I support clients who want a caring and steady space where they can explore their inner world with honesty and compassion.”</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/andrea-faraday?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anger management', 'Anxiety', 'Depression', 'End of life care']</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>['Empowering', 'Holistic', 'Open-minded']</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Cleopatra Oubre</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>“My communication style is warm, direct, and collaborative. I aim to create a safe, shame-free space where you feel heard and validated.”</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/cleopatra-oubre?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Bipolar disorder', 'Depression', 'Identity issues']</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Direct', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Renee EB-Walton</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>“My training enables me to facilitate personal growth and self-discovery, helping individuals access their inner resources to overcome challenges and reduce suffering.”</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/renee-eb-walton?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anger management', 'Anxiety', 'Depression', 'Family issues']</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>['Inquisitive', 'Solution-oriented', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Diana (Didi) Orozco</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>“My style is warm, down-to-earth, and collaborative. I believe therapy works best when it feels like a safe enough space where you can show up exactly as you are—tears, laughter, uncertainty, and all.”</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/diana-didi-orozco?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression', 'Identity issues']</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>['Empowering', 'Open-minded', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Dr. Peter Cabrera-Nguyen</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>“I aim to create a warm, collaborative space where you feel supported, understood, and empowered to make meaningful change.”</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/peter-cabrera-nguyen?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Bipolar disorder']</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Open-minded', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Michael Herrera</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>“I am warm, friendly, and passionate about my work. I am creative in techniques and I use humor to facilitate the exploration of concerns.”</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/michael-herrera?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Cultural &amp; ethnic issues']</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>['Challenging', 'Humorous', 'Participatory']</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Taylor Jackman</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>“I am a compassionate, trauma-informed therapist dedicated to creating a safe, affirming, and supportive space where clients feel genuinely seen and heard.”</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/taylor-jackman?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anger management', 'Anxiety', 'Chronic conditions', 'Depression']</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Empowering', 'Open-minded']</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Federico Rolandi</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>“I specialize in supporting high-functioning adults navigating ADHD, burnout, addiction, and emotional overwhelm. My approach is direct, compassionate, and focused on helping you understand how your mind works—while building practical tools that...”</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/federico-rolandi?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Bipolar disorder']</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>['Empowering', 'Energetic', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>George Brian Michalko</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>“I balance CBT and Psychodynamic principals through an LGBT Affirmative Lens to ensure my clients are able to identify internal and external stressors and find ways to move through them.”</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/george-brian-michalko?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Bipolar disorder', 'Cultural &amp; ethnic issues', 'Depression']</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Creative', 'Humorous']</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Merle Yost</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>“I am a survivor of emotional, sexual, and physical abuse... Through the intervention of close friends, I was encouraged to see a psychotherapist, and she changed my life.”</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/merle-yost?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Family issues', 'Identity issues', "Men's issues"]</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>['Challenging', 'Empowering', 'Holistic']</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Cheyenne Robbins</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>“I am passionate about this work because I believe psycho-education &amp; understanding trauma's impact on our mind, body, and soul is the pathway to ending generational cycles of abuse and creating bright and joyful futures.”</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/cheyenne-robbins?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Chronic conditions', 'Cultural &amp; ethnic issues', 'Depression']</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Creative', 'Open-minded']</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Dr. Emily Eckstein</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>“I believe therapy is most effective when you feel genuinely understood, supported, and challenged in ways that promote meaningful growth.”</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/emily-eckstein-2?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Bipolar disorder', 'Chronic conditions', 'Cultural &amp; ethnic issues']</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>['Direct', 'Open-minded', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>M. Watson</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>“I'm a Licensed Clinical Social Worker (LCSW) based in Long Beach, California, and I work with individual adults navigating life transitions, everyday stress, and everything in between. My background in older adult services means I bring a deep...”</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/m-watson?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'End of life care', 'PTSD', 'Stress management']</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Creative', 'Humorous']</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Maya Peters</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>“My treatment methodology builds on each individual's strengths. I see treatment as a collaborative endeavor that requires empathy, transparency, and client-centered goals.”</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/maya-peters-2?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anger management', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression']</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>['Empowering', 'Open-minded', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Christiana Metzenbaum</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>“With over a decade of experience as a licensed therapist, I've worked in varying settings with diverse populations. My specialty areas include anxiety, depression, trauma, ADHD, and relational issues with family, partners, work peers, and friends....”</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/christiana-metzenbaum?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Depression', 'End of life care']</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Humorous', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Stephanie DeLange</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>“I love getting down to the basics, the fundamentals, the practical action steps that can move someone from here to there.”</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/stephanie-delange?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Identity issues', 'Stress management', "Women's issues"]</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>['Empowering', 'Solution-oriented', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Spenser Kash</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>“I believe that even in the face of uncertainty, humans possess an inherent capacity for growth, resiliency, and healing.”</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/spenser-kash?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Depression', 'Grief or loss']</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Holistic', 'Open-minded']</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Alexandra Cooperman</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual &amp; in-person</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>“I am a Licensed Clinical Social Worker born and raised in Los Angeles, California. I earned my Bachelor’s in Psychology from Skidmore College and my Master of Social Work from Columbia University, where I specialized in clinical practice with...”</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/alexandra-cooperman?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Depression', 'Family issues']</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Empowering', 'Inquisitive']</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Dr. Lanz Banes</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>“I believe change begins with a strong therapeutic relationship. I prioritize creating an environment where clients can feel comfortable showing up as they are.”</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/lanz-banes?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Cultural &amp; ethnic issues']</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>['Empowering', 'Humorous', 'Inquisitive']</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Pavlo OConnor</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>“I work primarily with gay and queer men, and the people who love them, navigating identity, self-worth, relationships, and life transitions.”</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/pavlo-oconnor?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Cultural &amp; ethnic issues']</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Holistic', 'Solution-oriented']</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Nancy Lopez</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>“I balance insight and self-exploration with practical tools and strategies, helping clients develop a deeper understanding of themselves while working toward meaningful, achievable goals.”</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/nancy-lopez?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Depression', 'Grief or loss', 'Identity issues']</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Inquisitive', 'Open-minded']</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Jada Howcroft</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>“I specialize in LGBTQ+ affirming care and trauma-focused therapy. I believe in the power of relational healing...”</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/jada-howcroft?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Depression', 'Identity issues']</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>['Direct', 'Empowering', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Dimas Moncada</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>“I've developed the skills to help you (a) explore and identify the causes of your challenges and (b) develop an individualized plan that leads to measurable progress, the progress you seek.”</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/dimas-moncada?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression', 'End of life care']</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>['Holistic', 'Participatory', 'Solution-oriented']</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Jonathan Hernandez</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>“I am an LCSW with over 10 years of experience in the field. I've worked in hospital settings, inpatient and outpatient mental health, and telehealth therapy. I draw from a wide range of modalities to provide personalized therapeutic solutions and am...”</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/jonathan-hernandez?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Depression', 'End of life care']</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>['Empowering', 'Open-minded', 'Solution-oriented']</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Angie Noriega</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>“Hello, I am a Licensed Marriage and Family Therapist based in California. I received my Master's from the University of Southern California (USC) and have been practicing for 5 years. I help adults and teenagers be able to sift through negative...”</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/angie-noriega?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression', 'Family issues']</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Inquisitive', 'Open-minded']</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Leah Dean</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>“I'm continually driven by the belief that everyone has the potential for positive growth and change.”</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/leah-dean?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anger management', 'Anxiety', 'Depression', 'Family issues']</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Energetic', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Abneet Sohi</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>“My practice centers on empowering clients through challenges related to depression, anxiety, life transitions, and self-esteem.”</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/abneet-sohi?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression', 'Family issues']</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>['Direct', 'Empowering', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Elizabeth Hinojosa</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>“Liz's philosophy as a healer and alchemist is to honor each experience entrusted to her by offering a nonjudgemental space filled with empathy, compassion and sense of humor.”</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/elizabeth-hinojosa?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression', 'Family issues']</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>['Empowering', 'Humorous', 'Inquisitive']</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Damien Beauchemin</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>“I bring a lot of humor into my sessions because sometimes you need to laugh at the dark to remove its power.”</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/damien-beauchemin?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Bipolar disorder']</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>['Humorous', 'Participatory', 'Solution-oriented']</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Raquel Arellano-Jackson</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>“I believe real change is a gradual evolution (hence my practice name Gentle Evolutions), and there are often many stops along the way.”</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/raquel-arellano-jackson?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Bipolar disorder', 'Cultural &amp; ethnic issues', 'Depression']</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>['Inquisitive', 'Open-minded', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Betel Christy Ruschmeyer</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>“My name is Betel, and I am a California Licensed Marriage &amp; Family Therapist in my 6th year of practice. I received my MA from the California Institute of Integral Studies in San Francisco, where I trained in a process-oriented,...”</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/betel-christy-ruschmeyer?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Chronic conditions', 'Depression']</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>['Inquisitive', 'Open-minded', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Laura Myer</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>“I believe that daily habits and lifestyle play a vital role in overall wellness, including mental health.”</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/laura-myer?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Bipolar disorder', 'Chronic conditions']</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>['Holistic', 'Open-minded', 'Participatory']</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Be Staub</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual &amp; in-person</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>“As a Licensed Marriage &amp; Family Therapist and Registered Art Therapist, my work centers queer and transgender preteens, teens, and adults, as well as individuals with current or past foster care involvement. My clients may be feeling overwhelmed,...”</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/be-staub?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Depression', 'Family issues', 'Grief or loss']</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>['Creative', 'Inquisitive', 'Open-minded']</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Jaime Haasch</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>“I am warm, welcoming, and direct in my approach with clients. I include mindfulness, gratitude, compassion, and acceptance in my work with clients.”</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/jaime-haasch?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Depression']</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>['Empowering', 'Solution-oriented', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Tanya Fernandez</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>“I believe deep down we all have the wisdom we need—sometimes we just need a safe, compassionate space to reconnect with it.”</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/tanya-fernandez?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Family issues', 'Grief or loss', 'Identity issues']</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Empowering', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Essy Knopf</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>“My style is warm, direct, and emotionally attuned. I'm not a blank slate, and I don't expect you to be.”</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/essy-knopf?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Chronic conditions', 'Depression']</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>['Direct', 'Solution-oriented', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>David Washington</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>“Plants don't force growth — they respond to the right conditions. I believe people work the same way.”</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/david-washington?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anger management', 'Anxiety', 'Bipolar disorder', 'Cultural &amp; ethnic issues']</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>['Humorous', 'Open-minded', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Valentina Volk</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>“If you are navigating grief, a serious illness, a cancer diagnosis, or the quiet exhaustion of caring for someone you love, I am here for the full weight of it. I also work with people moving through anxiety, depression, infertility, and major life...”</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/valentina-volk?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anger management', 'Anxiety', 'Chronic conditions', 'Cultural &amp; ethnic issues']</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>['Empowering', 'Open-minded', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Adam Wiswell</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Psychologist, Virtual</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>“My approach to counseling is strengths based and empowerment focused. I use a collaborative and egalitarian style with people who I works with in counseling.”</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/adam-wiswell?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Cultural &amp; ethnic issues']</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>['Empowering', 'Humorous', 'Solution-oriented']</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Jeannette Phelan</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>“I've been a licensed LMFT in Sacramento, CA. for over 40 years. My primary education was at California State University, Sacramento, but have received extensive training in other areas that include, but not limited to: PTSD, Depression, Anxiety,...”</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/jeannette-phelan?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Depression', 'End of life care', 'Grief or loss']</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Direct', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Edward Garren</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>“The purpose of therapy is to remove blocks to truth; to help you abandon any patterns of belief that no longer serve you in a productive way; to implement self-forgiveness.”</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/edward-garren?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Cultural &amp; ethnic issues']</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>['Direct', 'Humorous', 'Participatory']</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Elihu "Eliott" Goretsky</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>“I specialize in adults with addiction-recovery issues, LGBT+ patients, phase of life problems, and couples (limited).”</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/elihu-eliott-goretsky?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression', 'End of life care']</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>['Empowering', 'Humorous', 'Solution-oriented']</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Gino Memoli</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>“I believe every part of you exists for a reason—even the ones that feel messy or hard to understand.”</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/gino-memoli?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Bipolar disorder', 'Depression', 'Family issues']</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>['Direct', 'Empowering', 'Open-minded']</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Shanelle Johnson</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual &amp; in-person</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>“I show up 100% authentic to who I am with the hopes that that give you permission to show up 100% authentic to who I am.”</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/shanelle-johnson?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Bipolar disorder']</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>['Direct', 'Empowering', 'Solution-oriented']</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Jacqueline Berrios</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>“I’m Jackie Berrios, a bilingual Licensed Clinical Social Worker (LCSW) with over a decade of experience in mental health. I'm a mother of two toddler boys, and a proud first-generation Latina from the DC area, living in CA since 2013. I help mom's...”</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/jacqueline-berrios?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Depression', 'Maternal mental health', 'Stress management']</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Empowering', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Alan Murray</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>“I believe therapy is a journey of self-discovery, empowerment, and healing, and I will be honored to walk that journey with you.”</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/alan-murray?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Chronic conditions', 'Cultural &amp; ethnic issues', 'Depression']</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>['Empowering', 'Holistic', 'Solution-oriented']</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Aaron Ruiz Zuniga</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>“I have extensive history working with individuals experiencing psychotic symptoms and crisis situations.”</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/aaron-ruiz-zuniga?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Bipolar disorder']</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>['Empowering', 'Humorous', 'Participatory']</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Margie Tyrone</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>“Margie Tyrone is a licensed marriage and family therapist (LMFT) with over 20 years of experience providing compassionate and effective therapy to individuals, couples, and families. With a deep passion for helping people navigate life’s challenges,...”</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/margie-tyrone?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Depression', 'Family issues', 'Grief or loss']</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>['Open-minded', 'Solution-oriented', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Patricia Riley</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>“I believe in each individual's right to self determination. Life can have multiple challenges, but with a thoughtful approaches it can reduce the power over us the challenges can have.”</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/patricia-riley?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Bipolar disorder']</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Open-minded', 'Solution-oriented']</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Cecilia Hanono</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>“My approach to therapy is warm, collaborative, and client-centered. I provide a safe, nonjudgmental space where clients feel truly heard and supported.”</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/cecilia-hanono?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Bipolar disorder']</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>['Empowering', 'Open-minded', 'Participatory']</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Rafael Ortega</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>“My goal is to create a space where you feel seen, understood, and supported as you navigate life's challenges.”</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/rafael-ortega?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Bipolar disorder']</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>['Empowering', 'Solution-oriented', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Stuart Riskin</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual &amp; in-person</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>“I bring a grounded, compassionate approach to therapy that's shaped by decades of working with individuals, couples, and families across the lifespan and across diverse life experiences.”</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/stuart-riskin?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Depression', 'Family issues']</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>['Challenging', 'Empowering', 'Solution-oriented']</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Marty Malin</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>“I have a special interest in working with people who struggle with issues related to gender experience, sexual practices and orientations outside the mainstream, LGBTQIA+ concerns, and disorders of sex development (DSD or intersex).”</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/marty-malin?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Chronic conditions']</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>['Empowering', 'Open-minded', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Sylvie Oconnell</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>“I have worked with clients on issues related to gender/identity challenges, substance use disorders, incarceration, social systems and adoption as well as collaborated extensively with law-enforcement/first responders and military service members.”</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/sylvie-oconnell?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Bipolar disorder', 'Depression', 'Family issues']</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>['Humorous', 'Open-minded', 'Solution-oriented']</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Carolyn DeTierra</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>“I'm a licensed Marriage and Family Therapist with over 25 years of experience supporting people through trauma, anxiety, depression, grief, substance use, and chronic stress.”</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/carolyn-detierra?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Bipolar disorder', 'Chronic conditions']</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Empowering', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Kory Doyle</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>“My specialty is working with LGBT+ adults and couples. Issues I have worked with in the past include same-sex couples' dynamics, self-acceptance, the coming-out process, and gender transition.”</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/kory-doyle?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Depression', 'Grief or loss']</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>['Open-minded', 'Solution-oriented', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Monica Castanon</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>“I consider myself a therapist who leads with empathy, making others feel safe, seen, and genuinely understood.”</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/monica-castanon?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Bipolar disorder']</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Empowering', 'Open-minded']</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Kerry Deeney</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>“I'm warm, real, and collaborative. You can expect open, judgment-free conversations that leave you feeling supported—and challenged in the best way—to grow and make changes that last.”</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/kerry-deeney?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Chronic conditions', 'Depression']</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>['Direct', 'Open-minded', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Dr. Tracy Griffith</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>“Seeking help can be the first step to acquire greater understanding and insight into our lives and relationships.”</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/tracy-griffith-2?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anger management', 'Chronic conditions', 'Depression', 'End of life care']</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>['Empowering', 'Open-minded', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>AJ (Amberle J) Wagner</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>“I believe therapy works best when it feels like a partnership, so I approach each session with curiosity, collaboration, and respect for your unique experiences.”</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/aj-amberle-j-wagner?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anger management', 'Anxiety', 'Depression', 'Family issues']</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Empowering', 'Solution-oriented']</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Gabriel Ramirez Penaranda</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>“I'm a Licensed Marriage and Family Therapist with 14 year experience in the mental health field. I specialize in supporting individuals who are committed to their emotional healing. I have experience in working with age groups ranging from children...”</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/gabriel-ramirez-penaranda?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression', 'Family issues']</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>['Empowering', 'Inquisitive', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Lonnie Ferguson</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>“Therapy is a courageous act of self love and it requires a collaborative approach to establish a sense of trust and safety.”</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/lonnie-ferguson?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Depression', 'End of life care']</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Inquisitive', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Kimberly Rios Lopez</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>“My goal is to create a supportive environment where you feel heard, respected, and empowered to move forward in ways that honor your identity and values.”</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/kimberly-rios-lopez?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Bipolar disorder']</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Empowering', 'Inquisitive']</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Elise Horwich</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>“My style is interactive, direct and supportive. I focus on the here and now but recognize that one's past impacts choices, feelings, and behaviors in the present.”</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/elise-horwich?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Chronic conditions']</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>['Empowering', 'Open-minded', 'Participatory']</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Brace Bacon</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual &amp; in-person</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>“I help adults navigate anxiety, self-esteem, relationship challenges, and life transitions with warmth, insight, and practical support.”</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/brace-bacon?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Chronic conditions', 'Depression', 'End of life care']</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>['Participatory', 'Solution-oriented', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Amy Annala</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>“I'm a LCSW providing telehealth out of Southern California. Growing up in Long Beach, I'm accustom to a variety of populations and personally have experience working in Addiction Medicine, with Child Welfare Services, and as an ally for my LGBTQ+...”</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/amy-annala?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anger management', 'Anxiety', 'Chronic conditions', 'Depression']</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Empowering', 'Participatory']</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Rebecca Marrs</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>“My approach is warm, collaborative, and focused on actually helping you feel better, not just talk about it.”</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/rebecca-marrs?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Bipolar disorder']</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Open-minded', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Dr. Thierry Kolpin</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Psychologist, Virtual</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>“With 30 years of experience as a therapist, I earned my Ph.D. in Counseling Psychology from Stanford University, specializing in school and community-based counseling. I'm dedicated to guiding clients through challenges like trauma, anxiety, and...”</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/thierry-kolpin?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Bipolar disorder']</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>['Empowering', 'Holistic', 'Solution-oriented']</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Patricia Gutierrez</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>“My practice centers on trauma and PTSD, identity and gender affirming care, and the lived experiences of women and LGBTQIA+ individuals.”</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/patricia-gutierrez-2?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Chronic conditions']</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>['Direct', 'Open-minded', 'Solution-oriented']</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Ashley Yen</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>“I believe that therapy is personal and each person is different, which is why my approach to therapy is client-led and meant to empower you.”</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/ashley-yen?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Bipolar disorder']</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Empowering', 'Open-minded']</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Dr. Chelsea Moss</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Psychologist, Virtual</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>“I'm passionate about providing evidence based and compassionate care to Black folks, particularly Black women.”</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/chelsea-moss?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Bipolar disorder', 'Cultural &amp; ethnic issues', 'Depression']</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>['Empowering', 'Open-minded', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Barbara Jean Douglass</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>“I am a Licensed Clinical Social Worker and PhD with 25 years experience working with adults, children and youth. My goal is to help you in your path towards feeling better, and experiencing an improved sense of confidence, self-esteem and...”</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/barbara-jean-douglass?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Chronic conditions', 'Cultural &amp; ethnic issues', 'Depression']</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Empowering', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Zora Speert Dieterich</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual &amp; in-person</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>“I am an interactive therapist whose practice involves a mutual cooperative approach to empower self-learning.”</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/zora-speert-dieterich?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anger management', 'Anxiety', 'Bipolar disorder', 'Chronic conditions']</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>['Empowering', 'Open-minded', 'Participatory']</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Shiva Banafti</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>“My work is grounded in a human-centered, trauma-informed approach, and one of my greatest strengths is the quality of therapeutic relationships I build with clients.”</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/shiva-banafti?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Bipolar disorder']</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>['Empowering', 'Holistic', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Minon Maier</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>“My approach to therapy is collaborative and focused on helping all clients feel safe and comfortable in sessions so that change is more likely to occur.”</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/minon-maier?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Depression']</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>['Direct', 'Empowering', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Sam Zia</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>“I am an AASECT-trained Sex Therapist. I have an MA in Clinical Psychology, and am a PhD Candidate in Human Sexuality.”</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/sam-zia?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression', 'Family issues']</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>['Humorous', 'Open-minded', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Jessica La Rocca</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>“I strive to create a space where you can feel emotionally safe, deeply understood, and supported without judgment.”</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/jessica-la-rocca?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Bipolar disorder']</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>['Empowering', 'Energetic', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Monica Lomeli</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>“My goal is to meet you where you are and work together to help you feel supported, understood, and empowered in your journey.”</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/monica-lomeli?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression', 'Family issues']</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Empowering', 'Open-minded']</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Elana Luban</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>“Hi! My greatest passion is working with individuals who wish to free themselves from trauma patterns, negative self-image, dopamine-seeking patterns, and depression. I'm certified in hypnotherapy, ketamine-assisted therapy, and EMDR, and use a...”</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/elana-luban?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Chronic conditions']</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>['Energetic', 'Inquisitive', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Katy Michaels</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual &amp; in-person</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>“As a member of a marginalized community myself I personally understand how hard it can be to reach out and ask for help.”</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/katy-michaels?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Bipolar disorder', 'Cultural &amp; ethnic issues']</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Empowering', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Jade Sustacek</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>“Seeking help and support can be so challenging, I know it's something I've struggled with personally. Through my experience as a licensed therapist, I've had the wonderful privilege of working in diverse settings helping individuals with a variety...”</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/jade-sustacek?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Depression', 'Eating disorders']</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>['Empowering', 'Open-minded', 'Solution-oriented']</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Kaitlin Kimmel</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>“I believe that true healing in psychotherapy requires digging deep to uncover the root causes of the challenge you're facing in this season of your life.”</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/kaitlin-kimmel?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Depression', 'Grief or loss', 'Identity issues']</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>['Creative', 'Direct', 'Open-minded']</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Alexándria Olosunde</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>“I believe you deserve a therapist who is fully human, fully present, and genuinely invested in your growth.”</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/alexandria-olosunde?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Bipolar disorder']</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>['Challenging', 'Humorous', 'Participatory']</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Kaitlyn Nguyen</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>“For the past 8 years I have partnered with clients on their journey towards healing and self-acceptance...”</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/kaitlyn-nguyen?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Family issues', "Men's issues", 'PTSD']</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Empowering', 'Inquisitive']</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Elisa Lewis</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>“I believe in empowering individuals and couples to live their best lives! I do this by being intentional and using a client-centered approach through an attachment lens.”</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/elisa-lewis?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression', 'End of life care']</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Empowering', 'Open-minded']</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Dr. Fei Yang</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>“I believe therapy is not only about symptom relief, but also about helping you feel more connected to yourself and the important relationships in your life.”</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/fei-yang?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Bipolar disorder']</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>['Empowering', 'Open-minded', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Caci Tassano</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>“Together we will work on, gain skills in working with and around emotional blocks and beliefs about themselves which are no longer useful to them.”</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/caci-tassano?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression']</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>['Creative', 'Holistic', 'Open-minded']</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Lauren Liu</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>“I'm passionate about supporting individuals as they navigate the complexities of identity, relationships, life transitions, trauma, and heavy emotions.”</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/lauren-liu?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anxiety', 'Cultural &amp; ethnic issues', 'Depression']</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Holistic', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Monique Kennedy</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>“My approach is warm, challenging, and empowering, focused on equipping clients with the tools they need to navigate life more effectively.”</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/monique-kennedy?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Panic disorders', 'PTSD', 'Relationship issues']</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Challenging', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Stephanie Guzman Alvarez</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>“My approach is warm, collaborative, and goal-oriented, helping clients build insight, resilience, and lasting tools for emotional well-being.”</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/stephanie-guzman-alvarez?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Cultural &amp; ethnic issues', 'Family issues', 'Identity issues']</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Empowering', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Eve Eichwald</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>“I'm your nerdy, thoughtful, and careful teammate—trained as a therapist—and you are the expert on yourself.”</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/eve-eichwald?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Chronic conditions', 'Depression', 'Grief or loss']</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>['Affirming', 'Inquisitive', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Bruce Strumpf</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>“I'll provide a supportive, nonjudgmental space where we can work together to help you feel better an move toward the life you want.”</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/bruce-strumpf?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Bipolar disorder', 'Chronic conditions', 'Depression']</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>['Humorous', 'Participatory', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Gaudi Alvarado</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>“I believe every person has an innate capacity to heal, and I consider it a privilege to walk alongside my clients as they reconnect with their strengths, resilience, and sense of self.”</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/gaudi-alvarado?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anxiety', 'Chronic conditions', 'Cultural &amp; ethnic issues', 'Depression']</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>['Empowering', 'Open-minded', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Sophia Kubes</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>“If you’re struggling with your relationship with food, your body, or feeling stuck in cycles of restriction, bingeing, or guilt, you are not alone—and you don’t have to face it by yourself. In my private practice, I specialize in working with...”</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/sophia-kubes?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'ADD/ADHD', 'Anger management', 'Anxiety', 'Bipolar disorder']</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>['Empowering', 'Open-minded', 'Solution-oriented']</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Mark Schiff</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>“My approach is warm, collaborative, and direct. I draw primarily from Acceptance and Commitment Therapy (ACT), along with elements of Cognitive Behavioral Therapy (CBT), to help clients develop greater flexibility in how they respond to difficult...”</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/mark-schiff?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Anger management', 'Anxiety', 'Chronic conditions', 'Cultural &amp; ethnic issues']</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>['Direct', 'Inquisitive', 'Warm']</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>DíAndré X</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Therapist, Virtual</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>“I am looking forward to working with people one-on-one so they can actually live life to the fullest, no matter who they are, where they come from, or how they choose to live.”</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>https://care.headway.co/providers/joshua-phillips?preferredCarrierId=61&amp;state=CALIFORNIA&amp;lat=32.7742488&amp;lon=-117.1411815</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>['Matches your filter: LGBTQIA+', 'Cultural &amp; ethnic issues', 'End of life care', 'Family issues', 'Grief or loss']</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>['Direct', 'Open-minded', 'Warm']</t>
         </is>
       </c>
     </row>
